--- a/Manual_Testing/Day2/Shaadi_application/ShaadiHomePage_Testing_Documentation.xlsx
+++ b/Manual_Testing/Day2/Shaadi_application/ShaadiHomePage_Testing_Documentation.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishnu Vardan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f43bb820658f1ef9/Desktop/BootCamp_Testing/Manual_Testing/Day2/Shaadi_application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EED315-5D2A-49B2-A7FB-06EC0A24C98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{89EED315-5D2A-49B2-A7FB-06EC0A24C98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE8E32E3-1DEB-47D7-B788-69E9577C95B1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TestCase_Amazon_Homepage" sheetId="9" r:id="rId1"/>
+    <sheet name="TestCase_Shaadi_Homepage" sheetId="9" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="95">
   <si>
     <t>Project Name:</t>
   </si>
@@ -111,24 +111,6 @@
     <t xml:space="preserve">Verify user can login with valid credentials  </t>
   </si>
   <si>
-    <t>1. User should open Microsoft Edge browser  
-2. User should navigate to https://www.amazon.in/  
-3. User should click on “Account &amp; Lists” / “Sign In” option on the Amazon homepage  
-4. User should enter valid Email ID/Mobile Number and Password  
-5. User should click on Login button</t>
-  </si>
-  <si>
-    <t>Url: https://www.amazon.in/  
-Mobile: 909******
-Password: ******</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User should be logged in successfully and Amazon homepage/account page should be displayed  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">User logged in successfully and Amazon homepage/account page is displayed </t>
-  </si>
-  <si>
     <t>Req_1.2</t>
   </si>
   <si>
@@ -138,23 +120,6 @@
     <t xml:space="preserve">Verify user can search for a product  </t>
   </si>
   <si>
-    <t>1. User should open Microsoft Edge browser  
-2. User should navigate to https://www.amazon.in/  
-3. User should locate the search bar on the Amazon homepage  
-4. User should enter a product name (e.g., Mobile, Laptop, Headphones)  
-5. User should click on Search icon or press Enter</t>
-  </si>
-  <si>
-    <t>Url: https://www.amazon.in/  
-Search Item: Mobile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User should see a list of relevant products based on the search query </t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is able to view search results for the entered product successfully </t>
-  </si>
-  <si>
     <t>Req_1.3</t>
   </si>
   <si>
@@ -164,20 +129,6 @@
     <t xml:space="preserve">Verify user can view orders  </t>
   </si>
   <si>
-    <t>1. User should open Microsoft Edge browser  
-2. User should navigate to https://www.amazon.in/  
-3. User should click on 'Returns &amp; Orders' option</t>
-  </si>
-  <si>
-    <t>Url: https://www.amazon.in/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orders page should be displayed </t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is successfully able to view orders page  </t>
-  </si>
-  <si>
     <t>Req_1.4</t>
   </si>
   <si>
@@ -187,24 +138,6 @@
     <t xml:space="preserve">Verify user can update delivery location  </t>
   </si>
   <si>
-    <t>1. User should open Microsoft Edge browser  
-2. User should navigate to https://www.amazon.in/  
-3. User should click on “Update location” option on the homepage  
-4. User should enter valid pincode (e.g., 400017)  
-5. User should click on Apply/Continue button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Url: https://www.amazon.in/  
-Location: Bhubaneswar 751002
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location should be updated successfully and delivery details should reflect the new pincode </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location is successfully updated and delivery location is displayed as entered  </t>
-  </si>
-  <si>
     <t>Req_1.5</t>
   </si>
   <si>
@@ -214,24 +147,6 @@
     <t xml:space="preserve">Verify user can change language on Amazon  </t>
   </si>
   <si>
-    <t>1. User should open Microsoft Edge browser  
-2. User should navigate to https://www.amazon.in/  
-3. User should click on the language option (EN icon) on the top navigation bar  
-4. User should select a preferred language (e.g., Hindi, Tamil, Telugu, Kannada, Malayalam, Bengali, Marathi)  
-5. User should click on Save/Apply changes</t>
-  </si>
-  <si>
-    <t>Url: https://www.amazon.in/  
-Default Language: English (EN)  
-Selected Language: Hindi (HI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selected language should be applied successfully and content should be displayed in the chosen language </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Language is successfully changed and website content is displayed in selected language </t>
-  </si>
-  <si>
     <t>Req_1.6</t>
   </si>
   <si>
@@ -241,43 +156,10 @@
     <t xml:space="preserve">Verify user can navigate to cart  </t>
   </si>
   <si>
-    <t>1. User should open Microsoft Edge browser  
-2. User should navigate to https://www.amazon.in/  
-3. User should click on Cart icon on the top-right corner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User should be redirected to cart page </t>
-  </si>
-  <si>
-    <t>User is successfully redirected to the cart page and all added items are displayed</t>
-  </si>
-  <si>
     <t>Req_1.7</t>
   </si>
   <si>
     <t>TC_08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verify user can sign out from Amazon account  
-</t>
-  </si>
-  <si>
-    <t>1. User should open Microsoft Edge browser  
-2. User should navigate to https://www.amazon.in/  
-3. User should click on “Account &amp; Lists” option on the top-right corner  
-4. User should click on “Sign Out” from the dropdown menu</t>
-  </si>
-  <si>
-    <t>Url: https://www.amazon.in/  
-User: Logged in user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User should be logged out successfully and redirected to the homepage  
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User is successfully logged out and redirected to the Amazon homepage  
-</t>
   </si>
   <si>
     <t>Mapping Test Scenarios with Test Cases (Shaadi Home page )</t>
@@ -327,12 +209,197 @@
 9. User should enter the OTP (One-Time Password) sent to the mobile number  
 10. User should click on “Verify” / “Create your Shaadi account"</t>
   </si>
+  <si>
+    <t xml:space="preserve">Verify user can sign out from Shaadi account  
+</t>
+  </si>
+  <si>
+    <t>Url: https://www.shaadi.com/  
+User: Logged in user</t>
+  </si>
+  <si>
+    <t>Url: https://www.shaadi.com/</t>
+  </si>
+  <si>
+    <t>Url: https://www.shaadi.com/  
+Mobile: 909******
+Password: ******</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be logged in successfully andshaadi.com homepage/account page should be displayed  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">User logged in successfully and shaadi homepage/account page is displayed </t>
+  </si>
+  <si>
+    <t>User should open Microsoft Edge browser.
+User should navigate to https://www.shaadi.com/
+User should click on Login/Sign In.
+User should enter registered email/mobile number.
+User should enter the correct password.
+User should click on Login.
+User should observe the home/profile page</t>
+  </si>
+  <si>
+    <t>User should login with valid credentials.
+User should navigate to Search/Matches.
+User should select the preferred age range.
+User should select preferred location.
+User should select other available preferences.
+User should click on Search/Apply Filters.
+User should observe the search results.</t>
+  </si>
+  <si>
+    <t>User should login successfully.
+User should navigate to Search/Matches.
+User should select any available profile.
+User should click on View Profile.
+User should observe the profile information.</t>
+  </si>
+  <si>
+    <t>User should login successfully.
+User should search for a suitable profile.
+User should open the selected profile.
+User should click on Interest/Send Interest.
+User should confirm the action if prompted.
+User should observe the interest status.</t>
+  </si>
+  <si>
+    <t>User should login to the test account.
+User should open Interests/Requests.
+User should select an incoming interest.
+User should click on Accept.
+User should observe the updated status.</t>
+  </si>
+  <si>
+    <t>User should login successfully.
+User should open My Profile.
+User should select Edit Profile.
+User should update a permitted profile field.
+User should click Save/Submit.
+User should reopen the profile.
+User should verify the updated information.</t>
+  </si>
+  <si>
+    <t>Age: 24–30
+Location: Bengaluru
+Education: Graduate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System should display profiles matching the selected search preferences. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relevant profiles displayed according to selected filters. </t>
+  </si>
+  <si>
+    <t>Active test member profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selected member's profile should open and available profile information should be displayed correctly. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profile details displayed successfully. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active test profile
+</t>
+  </si>
+  <si>
+    <t>Interest should be sent successfully and appropriate confirmation/status should be displayed.</t>
+  </si>
+  <si>
+    <t>Interest sent successfully.</t>
+  </si>
+  <si>
+    <t>Valid test request</t>
+  </si>
+  <si>
+    <t>Selected interest should be accepted and the interest status should be updated.</t>
+  </si>
+  <si>
+    <t>City: Hyderabad
+About Me: Software Professional</t>
+  </si>
+  <si>
+    <t>Updated profile information should be saved successfully and displayed on the user's profile.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User logged out successfully and redirected to the login page.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User should be logged out successfully and redirected to the public/login page. Authenticated content should not remain accessible.
+</t>
+  </si>
+  <si>
+    <t>Valid JPG/PNG image
+Size: Within application limit</t>
+  </si>
+  <si>
+    <t>Valid profile photo should be uploaded successfully and displayed on the user's profile.</t>
+  </si>
+  <si>
+    <t>Profile photo uploaded successfully.</t>
+  </si>
+  <si>
+    <t>TC_09</t>
+  </si>
+  <si>
+    <t>User should login successfully.
+User should open My Profile.
+User should click on profile photo/Edit Photo.
+User should select a valid image.
+User should upload the image.
+User should click Save.
+User should verify the profile photo.</t>
+  </si>
+  <si>
+    <t>User should login successfully.
+User should open a profile with an accepted/mutual connection.
+User should select the available communication option.
+User should enter a valid message.
+User should click Send.
+User should verify the message status.</t>
+  </si>
+  <si>
+    <t>User should open Microsoft Edge browser.
+User should navigate to https://www.shaadi.com/
+User should login with valid credentials.
+User should open the account/profile menu.
+User should click on Logout/Sign Out.
+User should observe the resulting page.
+User should try to access the authenticated page using the browser Back button.</t>
+  </si>
+  <si>
+    <t>Verify user can use communication features after a permitted connection</t>
+  </si>
+  <si>
+    <t>Hello, I would like to know more about your profile.</t>
+  </si>
+  <si>
+    <t>Message should be sent successfully when communication is permitted for the selected connection.</t>
+  </si>
+  <si>
+    <t>Message sent successfully.</t>
+  </si>
+  <si>
+    <t>Verify user can upload a profile photo</t>
+  </si>
+  <si>
+    <t>Req_1.8</t>
+  </si>
+  <si>
+    <t>Req_1.9</t>
+  </si>
+  <si>
+    <t>TC_10</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -349,6 +416,11 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -373,7 +445,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -424,11 +496,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -476,6 +557,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -493,6 +580,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -693,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56385C81-1887-44C6-8013-2F0DE761D956}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -711,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="2"/>
@@ -721,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>2</v>
@@ -747,13 +838,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="14" x14ac:dyDescent="0.25">
@@ -771,7 +862,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="2"/>
@@ -781,7 +872,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
@@ -817,19 +908,19 @@
         <v>19</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>20</v>
@@ -838,7 +929,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>22</v>
       </c>
@@ -849,42 +940,42 @@
         <v>24</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>21</v>
@@ -892,165 +983,216 @@
     </row>
     <row r="12" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="H12" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="70" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="87.5" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="50" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>66</v>
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="14" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="1:8" ht="14" x14ac:dyDescent="0.25">
-      <c r="A18" s="12"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="14"/>
+    <row r="17" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="87.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="14" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
+      <c r="C19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="14"/>
     </row>
     <row r="20" spans="1:8" ht="14" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="14"/>
     </row>
     <row r="21" spans="1:8" ht="14" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+    </row>
+    <row r="22" spans="1:8" ht="14" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+    </row>
+    <row r="23" spans="1:8" ht="14" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>